--- a/artfynd/A 51980-2022 artfynd.xlsx
+++ b/artfynd/A 51980-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51980-2022 artfynd.xlsx
+++ b/artfynd/A 51980-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80493750</v>
+        <v>80493748</v>
       </c>
       <c r="B2" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>711911.6485264078</v>
+        <v>711912</v>
       </c>
       <c r="R2" t="n">
-        <v>6654026.106812837</v>
+        <v>6654026</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +746,9 @@
           <t>2019-09-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80493748</v>
+        <v>80493750</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99096</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,26 +790,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>219798</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>711911.6485264078</v>
+        <v>711912</v>
       </c>
       <c r="R3" t="n">
-        <v>6654026.106812837</v>
+        <v>6654026</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -871,19 +851,9 @@
           <t>2019-09-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-09-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,6 +881,474 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126124827</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borsten, NNV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>711866</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6653962</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Riklig.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Örtrik, kalkpåverkad granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3294416</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>700 m SSV-SV Älmsta vandrarhem, 100 m S Mossmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>711876</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6653976</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-05-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-05-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Trådfräkengrupp i det västra diket vid markvägen till Mossmyrens fotbollsplaner.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Dike vid markväg</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3295392</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98030</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>600 m SSV Älmsta vandrarhem, mellan Mossmyren och Borsten, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>711875</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6653975</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-05-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-05-07</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I det västra vägdiket på skogsbilvägen. Återfynd.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Vägdike, skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126124828</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99097</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223609</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine subsp. helleborine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Borsten, NNV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>711866</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6653962</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Väddö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Örtrik, kalkpåverkad granskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51980-2022 artfynd.xlsx
+++ b/artfynd/A 51980-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80493748</t>
         </is>
       </c>
     </row>
@@ -881,6 +891,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80493750</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126124827</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3294416</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1231,6 +1256,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3295392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1349,8 +1379,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126124828</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>